--- a/Sindhi Muslim/PPP Node Data/PPP Node Data Consolidated Data RFP & Schoolwise.xlsx
+++ b/Sindhi Muslim/PPP Node Data/PPP Node Data Consolidated Data RFP & Schoolwise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\PPP Node Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A14FB72-9819-4461-B069-E6219B852704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9538D7-1A64-492C-BB4D-397CB877AF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -607,7 +607,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -854,33 +854,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -897,8 +870,35 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1239,77 +1239,77 @@
       </c>
       <c r="S1" s="36"/>
       <c r="T1" s="36"/>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="V1" s="39" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="11" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="32" t="s">
+      <c r="A2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="33" t="s">
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="33" t="s">
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="32"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="39"/>
     </row>
     <row r="3" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="39"/>
       <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>97</v>
       </c>
       <c r="U3" s="1"/>
-      <c r="V3" s="32"/>
+      <c r="V3" s="39"/>
     </row>
     <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -7753,280 +7753,280 @@
       </c>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A124" s="37">
+      <c r="A124" s="28">
         <v>122</v>
       </c>
-      <c r="B124" s="38" t="s">
+      <c r="B124" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C124" s="38" t="s">
+      <c r="C124" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D124" s="38" t="s">
+      <c r="D124" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="E124" s="39" t="s">
+      <c r="E124" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="F124" s="40">
+      <c r="F124" s="31">
         <v>408170153</v>
       </c>
-      <c r="G124" s="40" t="s">
+      <c r="G124" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H124" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I124" s="40" t="s">
+      <c r="H124" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J124" s="43">
+      <c r="J124" s="34">
         <v>44644</v>
       </c>
-      <c r="K124" s="40">
-        <v>0</v>
-      </c>
-      <c r="L124" s="41">
+      <c r="K124" s="31">
+        <v>0</v>
+      </c>
+      <c r="L124" s="32">
         <v>258</v>
       </c>
-      <c r="M124" s="41">
+      <c r="M124" s="32">
         <v>267</v>
       </c>
-      <c r="N124" s="41">
+      <c r="N124" s="32">
         <f t="shared" si="6"/>
         <v>525</v>
       </c>
-      <c r="O124" s="41">
+      <c r="O124" s="32">
         <v>5</v>
       </c>
-      <c r="P124" s="41">
+      <c r="P124" s="32">
         <v>7</v>
       </c>
-      <c r="Q124" s="41">
+      <c r="Q124" s="32">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="R124" s="41">
+      <c r="R124" s="32">
         <v>1</v>
       </c>
-      <c r="S124" s="41">
+      <c r="S124" s="32">
         <v>8</v>
       </c>
-      <c r="T124" s="41">
+      <c r="T124" s="32">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="U124" s="41" t="s">
+      <c r="U124" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="V124" s="42">
+      <c r="V124" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A125" s="37">
+      <c r="A125" s="28">
         <v>123</v>
       </c>
-      <c r="B125" s="38" t="s">
+      <c r="B125" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C125" s="38" t="s">
+      <c r="C125" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D125" s="38" t="s">
+      <c r="D125" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="E125" s="39" t="s">
+      <c r="E125" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="F125" s="40">
+      <c r="F125" s="31">
         <v>408170128</v>
       </c>
-      <c r="G125" s="40" t="s">
+      <c r="G125" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="H125" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I125" s="40" t="s">
+      <c r="H125" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J125" s="40"/>
-      <c r="K125" s="40">
-        <v>0</v>
-      </c>
-      <c r="L125" s="41">
+      <c r="J125" s="31"/>
+      <c r="K125" s="31">
+        <v>0</v>
+      </c>
+      <c r="L125" s="32">
         <v>103</v>
       </c>
-      <c r="M125" s="41">
+      <c r="M125" s="32">
         <v>133</v>
       </c>
-      <c r="N125" s="41">
+      <c r="N125" s="32">
         <f t="shared" si="6"/>
         <v>236</v>
       </c>
-      <c r="O125" s="41">
+      <c r="O125" s="32">
         <v>4</v>
       </c>
-      <c r="P125" s="41">
+      <c r="P125" s="32">
         <v>2</v>
       </c>
-      <c r="Q125" s="41">
+      <c r="Q125" s="32">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="R125" s="41">
-        <v>0</v>
-      </c>
-      <c r="S125" s="41">
-        <v>0</v>
-      </c>
-      <c r="T125" s="41">
+      <c r="R125" s="32">
+        <v>0</v>
+      </c>
+      <c r="S125" s="32">
+        <v>0</v>
+      </c>
+      <c r="T125" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U125" s="41" t="s">
+      <c r="U125" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="V125" s="42">
+      <c r="V125" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A126" s="37">
+      <c r="A126" s="28">
         <v>124</v>
       </c>
-      <c r="B126" s="38" t="s">
+      <c r="B126" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C126" s="38" t="s">
+      <c r="C126" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D126" s="38" t="s">
+      <c r="D126" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="E126" s="39" t="s">
+      <c r="E126" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="F126" s="40">
+      <c r="F126" s="31">
         <v>408170079</v>
       </c>
-      <c r="G126" s="40" t="s">
+      <c r="G126" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="H126" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I126" s="40" t="s">
+      <c r="H126" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J126" s="40"/>
-      <c r="K126" s="40">
-        <v>0</v>
-      </c>
-      <c r="L126" s="41">
+      <c r="J126" s="31"/>
+      <c r="K126" s="31">
+        <v>0</v>
+      </c>
+      <c r="L126" s="32">
         <v>212</v>
       </c>
-      <c r="M126" s="41">
+      <c r="M126" s="32">
         <v>242</v>
       </c>
-      <c r="N126" s="41">
+      <c r="N126" s="32">
         <f t="shared" si="6"/>
         <v>454</v>
       </c>
-      <c r="O126" s="41">
+      <c r="O126" s="32">
         <v>7</v>
       </c>
-      <c r="P126" s="41">
+      <c r="P126" s="32">
         <v>3</v>
       </c>
-      <c r="Q126" s="41">
+      <c r="Q126" s="32">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="R126" s="41">
-        <v>0</v>
-      </c>
-      <c r="S126" s="41">
-        <v>0</v>
-      </c>
-      <c r="T126" s="41">
+      <c r="R126" s="32">
+        <v>0</v>
+      </c>
+      <c r="S126" s="32">
+        <v>0</v>
+      </c>
+      <c r="T126" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U126" s="41" t="s">
+      <c r="U126" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="V126" s="42">
+      <c r="V126" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A127" s="37">
+      <c r="A127" s="28">
         <v>125</v>
       </c>
-      <c r="B127" s="38" t="s">
+      <c r="B127" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C127" s="38" t="s">
+      <c r="C127" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D127" s="38" t="s">
+      <c r="D127" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="E127" s="39" t="s">
+      <c r="E127" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="F127" s="40">
+      <c r="F127" s="31">
         <v>408170018</v>
       </c>
-      <c r="G127" s="40" t="s">
+      <c r="G127" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I127" s="40" t="s">
+      <c r="H127" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J127" s="40"/>
-      <c r="K127" s="40">
-        <v>0</v>
-      </c>
-      <c r="L127" s="41">
+      <c r="J127" s="31"/>
+      <c r="K127" s="31">
+        <v>0</v>
+      </c>
+      <c r="L127" s="32">
         <v>46</v>
       </c>
-      <c r="M127" s="41">
+      <c r="M127" s="32">
         <v>65</v>
       </c>
-      <c r="N127" s="41">
+      <c r="N127" s="32">
         <f t="shared" si="6"/>
         <v>111</v>
       </c>
-      <c r="O127" s="41">
+      <c r="O127" s="32">
         <v>1</v>
       </c>
-      <c r="P127" s="41">
+      <c r="P127" s="32">
         <v>2</v>
       </c>
-      <c r="Q127" s="41">
+      <c r="Q127" s="32">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="R127" s="41">
-        <v>0</v>
-      </c>
-      <c r="S127" s="41">
-        <v>0</v>
-      </c>
-      <c r="T127" s="41">
+      <c r="R127" s="32">
+        <v>0</v>
+      </c>
+      <c r="S127" s="32">
+        <v>0</v>
+      </c>
+      <c r="T127" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U127" s="41" t="s">
+      <c r="U127" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="V127" s="42">
+      <c r="V127" s="33">
         <v>0</v>
       </c>
     </row>
@@ -8569,6 +8569,11 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
@@ -8584,11 +8589,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="V1:V3"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G120 G122:G148" xr:uid="{00000000-0002-0000-0000-000001000000}">
